--- a/temp/Декларации/Табл-1.xlsx
+++ b/temp/Декларации/Табл-1.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB1CE7E4-5C5A-46EC-88AE-A30152EDAF18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{753D3237-C621-435C-B6A5-48968982C343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3950" yWindow="20" windowWidth="15250" windowHeight="10060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -124,7 +124,7 @@
     <numFmt numFmtId="164" formatCode="0_ "/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -184,13 +184,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="24"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -299,7 +292,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -363,43 +356,35 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -762,20 +747,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="61.5" x14ac:dyDescent="0.7">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
     </row>
     <row r="2" spans="1:14" ht="63.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A2" s="2" t="s">
@@ -814,10 +799,10 @@
       <c r="L2" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="28" t="s">
+      <c r="M2" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="28" t="s">
+      <c r="N2" s="27" t="s">
         <v>22</v>
       </c>
     </row>
@@ -825,7 +810,7 @@
       <c r="A3" s="8">
         <v>3</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="28" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="8" t="s">
@@ -849,10 +834,10 @@
       <c r="J3" s="13"/>
       <c r="K3" s="13"/>
       <c r="L3" s="13"/>
-      <c r="M3" s="30">
+      <c r="M3" s="12">
         <v>3</v>
       </c>
-      <c r="N3" s="31" t="s">
+      <c r="N3" s="12" t="s">
         <v>23</v>
       </c>
     </row>
@@ -872,75 +857,78 @@
       <c r="J4" s="24"/>
       <c r="K4" s="24"/>
       <c r="L4" s="24"/>
-      <c r="M4" s="27"/>
-    </row>
-    <row r="5" spans="1:14" s="41" customFormat="1" x14ac:dyDescent="0.7">
-      <c r="A5" s="33">
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+    </row>
+    <row r="5" spans="1:14" s="36" customFormat="1" x14ac:dyDescent="0.7">
+      <c r="A5" s="29">
         <v>1</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="36">
+      <c r="D5" s="32">
         <v>96</v>
       </c>
-      <c r="E5" s="37">
+      <c r="E5" s="33">
         <v>8.25</v>
       </c>
-      <c r="F5" s="38">
+      <c r="F5" s="34">
         <f>D5*E5</f>
         <v>792</v>
       </c>
-      <c r="G5" s="33" t="s">
+      <c r="G5" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="H5" s="39">
+      <c r="H5" s="35">
         <v>70002.080000000002</v>
       </c>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39"/>
-      <c r="K5" s="39">
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35">
         <v>88.386399999999995</v>
       </c>
-      <c r="L5" s="39"/>
-      <c r="M5" s="40"/>
-    </row>
-    <row r="6" spans="1:14" s="41" customFormat="1" x14ac:dyDescent="0.7">
-      <c r="A6" s="33">
+      <c r="L5" s="35"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+    </row>
+    <row r="6" spans="1:14" s="36" customFormat="1" x14ac:dyDescent="0.7">
+      <c r="A6" s="29">
         <v>2</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="35" t="s">
+      <c r="C6" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="36">
+      <c r="D6" s="32">
         <v>108</v>
       </c>
-      <c r="E6" s="37">
+      <c r="E6" s="33">
         <v>10.45</v>
       </c>
-      <c r="F6" s="38">
+      <c r="F6" s="34">
         <f>D6*E6</f>
         <v>1128.5999999999999</v>
       </c>
-      <c r="G6" s="33" t="s">
+      <c r="G6" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="H6" s="39">
+      <c r="H6" s="35">
         <v>99752.960000000006</v>
       </c>
-      <c r="I6" s="39"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39">
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35">
         <v>88.386399999999995</v>
       </c>
-      <c r="L6" s="39"/>
-      <c r="M6" s="40"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.7">
       <c r="A7" s="8">
@@ -970,9 +958,10 @@
       <c r="J7" s="13"/>
       <c r="K7" s="13"/>
       <c r="L7" s="13"/>
-      <c r="M7" s="27">
+      <c r="M7" s="12">
         <v>1</v>
       </c>
+      <c r="N7" s="12"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.7">
       <c r="A8" s="8">
@@ -1008,9 +997,10 @@
       <c r="L8" s="18">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="M8" s="27">
+      <c r="M8" s="12">
         <v>4</v>
       </c>
+      <c r="N8" s="12"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.7">
       <c r="A9" s="19"/>
@@ -1028,7 +1018,8 @@
       <c r="J9" s="25"/>
       <c r="K9" s="25"/>
       <c r="L9" s="26"/>
-      <c r="M9" s="27"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.7">
       <c r="A10" s="8"/>
@@ -1043,7 +1034,8 @@
       <c r="J10" s="17"/>
       <c r="K10" s="17"/>
       <c r="L10" s="18"/>
-      <c r="M10" s="27"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.7">
       <c r="A11" s="8"/>
@@ -1058,7 +1050,8 @@
       <c r="J11" s="17"/>
       <c r="K11" s="17"/>
       <c r="L11" s="18"/>
-      <c r="M11" s="27"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.7">
       <c r="A12" s="8">
@@ -1088,9 +1081,10 @@
       <c r="J12" s="13"/>
       <c r="K12" s="13"/>
       <c r="L12" s="13"/>
-      <c r="M12" s="27">
+      <c r="M12" s="12">
         <v>2</v>
       </c>
+      <c r="N12" s="12"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.7">
       <c r="A13" s="19"/>
@@ -1108,7 +1102,8 @@
       <c r="J13" s="24"/>
       <c r="K13" s="24"/>
       <c r="L13" s="24"/>
-      <c r="M13" s="27"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.7">
       <c r="A14" s="8"/>
@@ -1123,7 +1118,8 @@
       <c r="J14" s="13"/>
       <c r="K14" s="13"/>
       <c r="L14" s="13"/>
-      <c r="M14" s="27"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.7">
       <c r="A15" s="8"/>
@@ -1138,7 +1134,8 @@
       <c r="J15" s="13"/>
       <c r="K15" s="13"/>
       <c r="L15" s="13"/>
-      <c r="M15" s="27"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.7">
       <c r="A16" s="13"/>
@@ -1162,7 +1159,8 @@
       <c r="L16" s="26">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="M16" s="27"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:L2" xr:uid="{00000000-0009-0000-0000-000000000000}">
